--- a/assets/docs/lop4/Am nhac - Lop 4.xlsx
+++ b/assets/docs/lop4/Am nhac - Lop 4.xlsx
@@ -645,7 +645,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 1: Âm thanh ngày mới — Vận dụng – Sáng tạo (Tổng kết chủ đề 1)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -780,7 +780,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 2: Giai điệu quê hương — Vận dụng – Sáng tạo (Tổng kết chủ đề 2)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu các bài đã học và một vài trích đoạn dân ca cùng vùng miền; HS nghe đoán tên bài
 Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm, vận động; GV quay lại rồi chiếu cho cả lớp xem
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ bản đồ hành chính Việt Nam và chủ quyền của Việt Nam đối với quần đảo Hoàng Sa, Trường Sa.</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 3: Thầy cô với chúng em — Vận dụng – Sáng tạo (Tổng kết chủ đề 3)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 4: Vui đón Tết — Vận dụng – Sáng tạo (Tổng kết chủ đề 4)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp — Vận dụng – Sáng tạo (Tổng kết chủ đề 5)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 6: Tình bạn tuổi thơ — Vận dụng – Sáng tạo (Tổng kết chủ đề 6)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1531,7 +1531,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài — Vận dụng – Sáng tạo (Tổng kết chủ đề 7)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
